--- a/artfynd/A 10626-2024 artfynd.xlsx
+++ b/artfynd/A 10626-2024 artfynd.xlsx
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117450054</v>
+        <v>117451843</v>
       </c>
       <c r="B15" t="n">
-        <v>90941</v>
+        <v>90499</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,25 +2098,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603286</v>
+        <v>603273</v>
       </c>
       <c r="R15" t="n">
-        <v>7027273</v>
+        <v>7027052</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117451462</v>
+        <v>117451675</v>
       </c>
       <c r="B17" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,28 +2307,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandåsberget (Sandåsberget), Ång</t>
@@ -2397,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117451843</v>
+        <v>117451754</v>
       </c>
       <c r="B18" t="n">
-        <v>90499</v>
+        <v>90464</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,25 +2413,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603273</v>
+        <v>603278</v>
       </c>
       <c r="R18" t="n">
-        <v>7027052</v>
+        <v>7027103</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2499,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117451416</v>
+        <v>117450054</v>
       </c>
       <c r="B19" t="n">
-        <v>90464</v>
+        <v>90941</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,25 +2515,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603262</v>
+        <v>603286</v>
       </c>
       <c r="R19" t="n">
-        <v>7027162</v>
+        <v>7027273</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2601,7 +2605,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117451754</v>
+        <v>117451416</v>
       </c>
       <c r="B20" t="n">
         <v>90464</v>
@@ -2641,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603278</v>
+        <v>603262</v>
       </c>
       <c r="R20" t="n">
-        <v>7027103</v>
+        <v>7027162</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2703,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117451675</v>
+        <v>117451462</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,32 +2719,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sandåsberget (Sandåsberget), Ång</t>

--- a/artfynd/A 10626-2024 artfynd.xlsx
+++ b/artfynd/A 10626-2024 artfynd.xlsx
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117451843</v>
+        <v>117451675</v>
       </c>
       <c r="B15" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,38 +2098,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sandåsberget (Sandåsberget), Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603273</v>
+        <v>603267</v>
       </c>
       <c r="R15" t="n">
-        <v>7027052</v>
+        <v>7027168</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2191,7 +2195,7 @@
         <v>117451709</v>
       </c>
       <c r="B16" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117451675</v>
+        <v>117450054</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>90943</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,38 +2315,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandåsberget (Sandåsberget), Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603267</v>
+        <v>603286</v>
       </c>
       <c r="R17" t="n">
-        <v>7027168</v>
+        <v>7027273</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117451754</v>
+        <v>117451462</v>
       </c>
       <c r="B18" t="n">
-        <v>90464</v>
+        <v>90501</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2413,25 +2413,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603278</v>
+        <v>603267</v>
       </c>
       <c r="R18" t="n">
-        <v>7027103</v>
+        <v>7027168</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117450054</v>
+        <v>117451416</v>
       </c>
       <c r="B19" t="n">
-        <v>90941</v>
+        <v>90466</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,25 +2515,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603286</v>
+        <v>603262</v>
       </c>
       <c r="R19" t="n">
-        <v>7027273</v>
+        <v>7027162</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2605,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117451416</v>
+        <v>117451754</v>
       </c>
       <c r="B20" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603262</v>
+        <v>603278</v>
       </c>
       <c r="R20" t="n">
-        <v>7027162</v>
+        <v>7027103</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117451462</v>
+        <v>117451843</v>
       </c>
       <c r="B21" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603267</v>
+        <v>603273</v>
       </c>
       <c r="R21" t="n">
-        <v>7027168</v>
+        <v>7027052</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
